--- a/GameData/DataTables/Core/EntityGroupTable.xlsx
+++ b/GameData/DataTables/Core/EntityGroupTable.xlsx
@@ -2,30 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="145621" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,20 +47,16 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -132,9 +129,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -172,7 +169,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -206,7 +203,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -241,10 +237,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -423,19 +418,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="2.5" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="12.75" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="5.25" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="10.5" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
-    <col width="17.25" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9.5" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
@@ -447,7 +433,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
@@ -457,7 +443,6 @@
           <t>ID</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Name</t>
@@ -468,7 +453,7 @@
           <t>ReleaseInterval</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
@@ -485,7 +470,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
@@ -495,7 +480,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>string</t>
@@ -506,7 +490,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -523,22 +507,41 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="0" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+          <t>Framework default entity groups</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>分组名称</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>自动释放间隔（秒），0 表示不自动释放</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>对象池容量，0 表示不限制</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>对象过期时间（秒），0 表示不过期</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>优先级，数值越大越晚被释放</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -607,35 +610,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>